--- a/SGC-CKN/Excel/43a45b2c-74ca-4492-bdf5-de22364c2bf3_Cọc_thí_nghiệm_TP-3_1500_21-03-2016.xlsx
+++ b/SGC-CKN/Excel/43a45b2c-74ca-4492-bdf5-de22364c2bf3_Cọc_thí_nghiệm_TP-3_1500_21-03-2016.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>16:25 20/03/2016</t>
+    <t>16:25 20/03/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>23:45 21/03/2016</t>
+    <t>23:45 21/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">16:25
-20/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t xml:space="preserve">16:45
-20/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">16:55
-20/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">11:15
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">14:22
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">15:14
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">17:00
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,14 +166,14 @@
   </si>
   <si>
     <t xml:space="preserve">19:10
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
     <t xml:space="preserve">23:45
-21/03/2016</t>
+20/03/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
